--- a/Templates/bulkImport/config/construct_NCR_config_sabah.xlsx
+++ b/Templates/bulkImport/config/construct_NCR_config_sabah.xlsx
@@ -4,17 +4,30 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12984"/>
+    <workbookView windowWidth="22188" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="ncr_raw" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="235">
   <si>
     <t>*</t>
   </si>
@@ -22,67 +35,379 @@
     <t>show</t>
   </si>
   <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
     <t>c_issued_by</t>
   </si>
   <si>
+    <t>c_ncr_type</t>
+  </si>
+  <si>
+    <t>c_type</t>
+  </si>
+  <si>
+    <t>c_work_discipline</t>
+  </si>
+  <si>
     <t>c_ref_no</t>
   </si>
   <si>
-    <t>c_type</t>
-  </si>
-  <si>
-    <t>c_work_discipline</t>
-  </si>
-  <si>
     <t>c_date_issued</t>
   </si>
   <si>
+    <t>c_issued_to_company</t>
+  </si>
+  <si>
+    <t>c_utility_provider</t>
+  </si>
+  <si>
+    <t>c_utility_provider_other</t>
+  </si>
+  <si>
+    <t>c_location</t>
+  </si>
+  <si>
+    <t>c_doc_reference</t>
+  </si>
+  <si>
     <t>c_description</t>
   </si>
   <si>
+    <t>c_attachment</t>
+  </si>
+  <si>
     <t>c_file</t>
   </si>
   <si>
+    <t>c_originated_by</t>
+  </si>
+  <si>
+    <t>c_lat</t>
+  </si>
+  <si>
+    <t>c_lon</t>
+  </si>
+  <si>
+    <t>c_action</t>
+  </si>
+  <si>
     <t>c_actioner</t>
   </si>
   <si>
     <t>c_action_date</t>
   </si>
   <si>
-    <t>c_action_status</t>
+    <t>c_status</t>
+  </si>
+  <si>
+    <t>c_draft_remark</t>
+  </si>
+  <si>
+    <t>c_draft_confirmed_by</t>
+  </si>
+  <si>
+    <t>c_draft_date</t>
+  </si>
+  <si>
+    <t>c_draft_time</t>
+  </si>
+  <si>
+    <t>c_review_action</t>
+  </si>
+  <si>
+    <t>c_verify_remark</t>
+  </si>
+  <si>
+    <t>c_confirmed_by</t>
+  </si>
+  <si>
+    <t>c_verified_date</t>
+  </si>
+  <si>
+    <t>c_verified_time</t>
+  </si>
+  <si>
+    <t>c_resub_remark</t>
+  </si>
+  <si>
+    <t>c_acknowledge</t>
+  </si>
+  <si>
+    <t>c_acknowledge_name</t>
+  </si>
+  <si>
+    <t>c_acknowledge_position</t>
+  </si>
+  <si>
+    <t>c_acknowledge_company</t>
+  </si>
+  <si>
+    <t>c_acknowledge_time</t>
+  </si>
+  <si>
+    <t>c_acknowledge_date</t>
+  </si>
+  <si>
+    <t>c_root_cause</t>
+  </si>
+  <si>
+    <t>c_disposition</t>
+  </si>
+  <si>
+    <t>c_preventive_action</t>
+  </si>
+  <si>
+    <t>c_further_details</t>
+  </si>
+  <si>
+    <t>c_proposal_attachment</t>
+  </si>
+  <si>
+    <t>c_actual_completion_date</t>
+  </si>
+  <si>
+    <t>c_completion_date</t>
+  </si>
+  <si>
+    <t>c_date_submitted</t>
+  </si>
+  <si>
+    <t>c_submitted_by</t>
+  </si>
+  <si>
+    <t>c_disposition_verification</t>
+  </si>
+  <si>
+    <t>c_review_remark</t>
+  </si>
+  <si>
+    <t>c_date_reviewed</t>
+  </si>
+  <si>
+    <t>c_agreed_by_sec1</t>
+  </si>
+  <si>
+    <t>c_date_agreed_sec1</t>
+  </si>
+  <si>
+    <t>c_agreed_designation</t>
+  </si>
+  <si>
+    <t>c_rfi_action</t>
+  </si>
+  <si>
+    <t>c_rfi_ref_no</t>
+  </si>
+  <si>
+    <t>c_rfi_revision_no</t>
+  </si>
+  <si>
+    <t>c_rfi_work_discipline</t>
+  </si>
+  <si>
+    <t>c_rfi_utility_provider</t>
+  </si>
+  <si>
+    <t>c_rfi_utility_provider_other</t>
+  </si>
+  <si>
+    <t>c_rfi_description</t>
+  </si>
+  <si>
+    <t>c_rfi_propose_date</t>
+  </si>
+  <si>
+    <t>c_rfi_propose_time</t>
+  </si>
+  <si>
+    <t>c_rfi_work_permit</t>
+  </si>
+  <si>
+    <t>c_rfi_work_permit_thirdParty</t>
+  </si>
+  <si>
+    <t>c_rfi_location</t>
+  </si>
+  <si>
+    <t>c_rfi_approved_ms</t>
+  </si>
+  <si>
+    <t>c_rfi_approved_inspect_test</t>
+  </si>
+  <si>
+    <t>c_rfi_file    </t>
+  </si>
+  <si>
+    <t>c_rfi_created_by</t>
+  </si>
+  <si>
+    <t>c_rfi_date_created</t>
+  </si>
+  <si>
+    <t>c_rfi_time_created</t>
+  </si>
+  <si>
+    <t>c_rfi_confirmed_by</t>
+  </si>
+  <si>
+    <t>c_rfi_lat</t>
+  </si>
+  <si>
+    <t>c_rfi_lon</t>
+  </si>
+  <si>
+    <t>c_rfi_actioner</t>
+  </si>
+  <si>
+    <t>c_rfi_action_date</t>
+  </si>
+  <si>
+    <t>c_rfi_status</t>
+  </si>
+  <si>
+    <t>c_rfi_acknowledge</t>
+  </si>
+  <si>
+    <t>c_rfi_acknowledge_name</t>
+  </si>
+  <si>
+    <t>c_rfi_acknowledge_position</t>
+  </si>
+  <si>
+    <t>c_rfi_acknowledge_company</t>
+  </si>
+  <si>
+    <t>c_rfi_acknowledge_time</t>
+  </si>
+  <si>
+    <t>c_rfi_acknowledge_date</t>
+  </si>
+  <si>
+    <t>c_rfi_acknowlegde_file</t>
+  </si>
+  <si>
+    <t>c_rfi_acknowledge_remarks</t>
+  </si>
+  <si>
+    <t>c_rfi_applicable_review</t>
+  </si>
+  <si>
+    <t>c_rfi_wir_approval_sabah</t>
+  </si>
+  <si>
+    <t>c_rfi_app_file</t>
+  </si>
+  <si>
+    <t>c_rfi_app_remarks</t>
+  </si>
+  <si>
+    <t>c_rfi_inspection_type</t>
+  </si>
+  <si>
+    <t>c_rfi_remarks</t>
+  </si>
+  <si>
+    <t>c_rfi_inspector</t>
+  </si>
+  <si>
+    <t>c_rfi_inspector_position</t>
+  </si>
+  <si>
+    <t>c_rfi_inspection_date</t>
+  </si>
+  <si>
+    <t>c_rfi_inspection_approval</t>
+  </si>
+  <si>
+    <t>c_rfi_inspection_approval_reason</t>
+  </si>
+  <si>
+    <t>c_rfi_inspection_unapproved_reason</t>
+  </si>
+  <si>
+    <t>c_rfi_inspection_remarks</t>
+  </si>
+  <si>
+    <t>c_rfi_inspection_app_file</t>
+  </si>
+  <si>
+    <t>c_rfi_require_document</t>
+  </si>
+  <si>
+    <t>c_rfi_date_approved</t>
+  </si>
+  <si>
+    <t>c_rfi_issued_by</t>
+  </si>
+  <si>
+    <t>c_rfi_time_issued</t>
+  </si>
+  <si>
+    <t>c_rfi_attachment_doc</t>
+  </si>
+  <si>
+    <t>c_rfi_doc_submitted_by</t>
+  </si>
+  <si>
+    <t>c_rfi_doc_submitted_date</t>
+  </si>
+  <si>
+    <t>c_rfi_doc_submitted_time</t>
+  </si>
+  <si>
+    <t>c_rfi_wir_doc_status</t>
+  </si>
+  <si>
+    <t>c_rfi_close_out_date</t>
+  </si>
+  <si>
+    <t>c_rfi_review_doc_file</t>
+  </si>
+  <si>
+    <t>c_rfi_review_doc_remarks</t>
+  </si>
+  <si>
+    <t>c_rfi_recommendation_act</t>
+  </si>
+  <si>
+    <t>c_rfi_recommend_remarks</t>
+  </si>
+  <si>
+    <t>c_rfi_recommend_by</t>
+  </si>
+  <si>
+    <t>c_rfi_recommend_date</t>
+  </si>
+  <si>
+    <t>c_rfi_verify_status</t>
+  </si>
+  <si>
+    <t>c_rfi_verify_file</t>
+  </si>
+  <si>
+    <t>c_rfi_verify_remarks</t>
+  </si>
+  <si>
+    <t>c_rfi_verify_by</t>
+  </si>
+  <si>
+    <t>c_rfi_verify_date</t>
+  </si>
+  <si>
+    <t>c_rfi_acknowledge_reject</t>
+  </si>
+  <si>
+    <t>c_rfi_acknowledge_reject_name</t>
+  </si>
+  <si>
+    <t>c_rfi_acknowledge_reject_position</t>
+  </si>
+  <si>
+    <t>c_rfi_acknowledge_reject_company</t>
+  </si>
+  <si>
+    <t>c_rfi_acknowledge_reject_time</t>
+  </si>
+  <si>
+    <t>c_rfi_acknowledge_reject_date</t>
   </si>
   <si>
     <t>c_wir_doc_status</t>
@@ -91,56 +416,343 @@
     <t>c_close_out_date</t>
   </si>
   <si>
+    <t>c_close_verification</t>
+  </si>
+  <si>
+    <t>c_verification_attachment</t>
+  </si>
+  <si>
+    <t>c_close_verified_by</t>
+  </si>
+  <si>
+    <t>c_close_verified_position</t>
+  </si>
+  <si>
+    <t>c_close_verified_time</t>
+  </si>
+  <si>
+    <t>c_close_verified_date</t>
+  </si>
+  <si>
     <t>Issued By</t>
   </si>
   <si>
+    <t>NCR Types</t>
+  </si>
+  <si>
+    <t>Types</t>
+  </si>
+  <si>
+    <t>Work Discipline</t>
+  </si>
+  <si>
     <t>NCR Ref No.</t>
   </si>
   <si>
-    <t>Types</t>
-  </si>
-  <si>
-    <t>Work Discipline</t>
-  </si>
-  <si>
     <t>Date Issued</t>
   </si>
   <si>
+    <t>Issued To (Company)</t>
+  </si>
+  <si>
+    <t>Utility Provider</t>
+  </si>
+  <si>
+    <t>Utility Provider Others</t>
+  </si>
+  <si>
+    <t>Location</t>
+  </si>
+  <si>
+    <t>Document Ref. (Spec/Dwg./etc)</t>
+  </si>
+  <si>
     <t>NCR Description</t>
   </si>
   <si>
+    <t>Attachment</t>
+  </si>
+  <si>
+    <t>File</t>
+  </si>
+  <si>
+    <t>Originated By</t>
+  </si>
+  <si>
+    <t>Latitude</t>
+  </si>
+  <si>
+    <t>Longitude</t>
+  </si>
+  <si>
+    <t>Action</t>
+  </si>
+  <si>
+    <t>Actioner Name</t>
+  </si>
+  <si>
+    <t>Action Date</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Draft Remarks</t>
+  </si>
+  <si>
+    <t>Draft Confirmed By</t>
+  </si>
+  <si>
+    <t>Draft Date</t>
+  </si>
+  <si>
+    <t>Draft Time</t>
+  </si>
+  <si>
+    <t>Draft Review Action</t>
+  </si>
+  <si>
+    <t>Draft Verification Remarks</t>
+  </si>
+  <si>
+    <t>Draft Verification Confirmed By</t>
+  </si>
+  <si>
+    <t>Draft Verification Date</t>
+  </si>
+  <si>
+    <t>Draft Verification Time</t>
+  </si>
+  <si>
+    <t>Draft Resubmission Remarks</t>
+  </si>
+  <si>
+    <t>Acknowledge</t>
+  </si>
+  <si>
+    <t>Acknowledge Name</t>
+  </si>
+  <si>
+    <t>Acknowledge Position</t>
+  </si>
+  <si>
+    <t>Acknowledge Company</t>
+  </si>
+  <si>
+    <t>Acknowledge Time</t>
+  </si>
+  <si>
+    <t>Acknowledge Date</t>
+  </si>
+  <si>
+    <t>Root Cause</t>
+  </si>
+  <si>
+    <t>Proposed Corrective Action</t>
+  </si>
+  <si>
+    <t>Proposed Preventive Action</t>
+  </si>
+  <si>
+    <t>Further Details (If any)</t>
+  </si>
+  <si>
     <t>Attachment(s)</t>
   </si>
   <si>
-    <t>Actioner Name</t>
-  </si>
-  <si>
-    <t>Action Date</t>
-  </si>
-  <si>
-    <t>Status</t>
+    <t>Actual Completion Date</t>
+  </si>
+  <si>
+    <t>Proposed Date By WPC</t>
+  </si>
+  <si>
+    <t>Proposal Submitted Date</t>
+  </si>
+  <si>
+    <t>Proposed By</t>
+  </si>
+  <si>
+    <t>Acceptable Disposition</t>
+  </si>
+  <si>
+    <t>Disposition Review Comment</t>
+  </si>
+  <si>
+    <t>Disposition Review Date</t>
+  </si>
+  <si>
+    <t>Disposition Agreed By</t>
+  </si>
+  <si>
+    <t>Disposition Agreed Date</t>
+  </si>
+  <si>
+    <t>Disposition Agreed Designation</t>
+  </si>
+  <si>
+    <t>RFI Ref. No.</t>
+  </si>
+  <si>
+    <t>Revision No.</t>
+  </si>
+  <si>
+    <t>Others (Please Specify)</t>
+  </si>
+  <si>
+    <t>Description of Work</t>
+  </si>
+  <si>
+    <t>Date of Inspection</t>
+  </si>
+  <si>
+    <t>Time of Inspection</t>
+  </si>
+  <si>
+    <t>Permit to Work (PTW)</t>
+  </si>
+  <si>
+    <t>Permit to Wor for Third Party</t>
+  </si>
+  <si>
+    <t>Location of Work (CH No. / gridline / structure element/etc.)</t>
+  </si>
+  <si>
+    <t>Method Statement for work has been approved?</t>
+  </si>
+  <si>
+    <t>Inspection &amp; Test Plan for work has been submitted and approved?</t>
+  </si>
+  <si>
+    <t>Submitter Name (WPC)</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Time</t>
+  </si>
+  <si>
+    <t>Confirmed By</t>
+  </si>
+  <si>
+    <t>Actioner</t>
+  </si>
+  <si>
+    <t>Action Status</t>
+  </si>
+  <si>
+    <t>Acknowledger Name</t>
+  </si>
+  <si>
+    <t>Acknowledger Position</t>
+  </si>
+  <si>
+    <t>Acknowledger Company</t>
+  </si>
+  <si>
+    <t>Remarks</t>
+  </si>
+  <si>
+    <t>Applicable for RE?</t>
+  </si>
+  <si>
+    <t>RFI Accepted for Inspection?</t>
+  </si>
+  <si>
+    <t>Type of Work Inspection</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Position</t>
+  </si>
+  <si>
+    <t>Inspection Approval</t>
+  </si>
+  <si>
+    <t>Reasons for Approved Inspection</t>
+  </si>
+  <si>
+    <t>Reasons for Unapproved/Rejected Inspection</t>
+  </si>
+  <si>
+    <t>Remarks (please state reasons)</t>
+  </si>
+  <si>
+    <t>Require Supporting Document?</t>
+  </si>
+  <si>
+    <t>Approved Date</t>
+  </si>
+  <si>
+    <t>Time Issued</t>
+  </si>
+  <si>
+    <t>Submitted By</t>
+  </si>
+  <si>
+    <t>Close Out Date</t>
+  </si>
+  <si>
+    <t>Recommend?</t>
+  </si>
+  <si>
+    <t>Recommended By</t>
+  </si>
+  <si>
+    <t>Verify?</t>
+  </si>
+  <si>
+    <t>Verified By</t>
+  </si>
+  <si>
+    <t>Acknowledge Reject?</t>
+  </si>
+  <si>
+    <t>Company</t>
   </si>
   <si>
     <t>Status (Doc)</t>
   </si>
   <si>
-    <t>Close Out Date</t>
+    <t>Close Verification</t>
+  </si>
+  <si>
+    <t>Close Verification Attachment(s)</t>
+  </si>
+  <si>
+    <t>Close Verification Name</t>
+  </si>
+  <si>
+    <t>Close Verification Position</t>
+  </si>
+  <si>
+    <t>Close Verification Time</t>
+  </si>
+  <si>
+    <t>Close Verification Date</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;RM&quot;* #,##0.00_-;\-&quot;RM&quot;* #,##0.00_-;_-&quot;RM&quot;* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;RM&quot;* #,##0_-;\-&quot;RM&quot;* #,##0_-;_-&quot;RM&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="41" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;RM&quot;* #,##0.00_-;\-&quot;RM&quot;* #,##0.00_-;_-&quot;RM&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;RM&quot;* #,##0_-;\-&quot;RM&quot;* #,##0_-;_-&quot;RM&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
       <charset val="134"/>
     </font>
@@ -599,154 +1211,156 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1095,35 +1709,297 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:ED5"/>
   <sheetFormatPr defaultColWidth="9.11111111111111" defaultRowHeight="14.4" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" width="11.1111111111111" style="1" customWidth="1"/>
-    <col min="2" max="4" width="11.6666666666667" style="1" customWidth="1"/>
-    <col min="5" max="5" width="13.6666666666667" style="1" customWidth="1"/>
-    <col min="6" max="6" width="15.4444444444444" style="1" customWidth="1"/>
-    <col min="7" max="7" width="13.1111111111111" style="1" customWidth="1"/>
-    <col min="8" max="8" width="14.4444444444444" style="1" customWidth="1"/>
-    <col min="9" max="9" width="13.4444444444444" style="1" customWidth="1"/>
-    <col min="10" max="10" width="8.11111111111111" style="1" customWidth="1"/>
-    <col min="11" max="11" width="9.11111111111111" style="1"/>
+    <col min="1" max="1" width="11.6666666666667" style="1" customWidth="1"/>
+    <col min="2" max="2" width="10.7777777777778" style="1" customWidth="1"/>
+    <col min="3" max="3" width="7.11111111111111" style="1" customWidth="1"/>
+    <col min="4" max="4" width="16.8888888888889" style="1" customWidth="1"/>
+    <col min="5" max="5" width="12.1111111111111" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.6666666666667" style="1" customWidth="1"/>
+    <col min="7" max="7" width="21" style="1" customWidth="1"/>
+    <col min="8" max="8" width="16.6666666666667" style="1" customWidth="1"/>
+    <col min="9" max="9" width="22.7777777777778" style="1" customWidth="1"/>
+    <col min="10" max="10" width="10.2222222222222" style="1" customWidth="1"/>
+    <col min="11" max="11" width="29.6666666666667" style="1" customWidth="1"/>
+    <col min="12" max="12" width="15.5555555555556" style="1" customWidth="1"/>
+    <col min="13" max="13" width="13.4444444444444" style="1" customWidth="1"/>
+    <col min="14" max="14" width="6.11111111111111" style="1" customWidth="1"/>
+    <col min="15" max="15" width="15.2222222222222" style="1" customWidth="1"/>
+    <col min="16" max="16" width="8.33333333333333" style="1" customWidth="1"/>
+    <col min="17" max="17" width="9.66666666666667" style="1" customWidth="1"/>
+    <col min="18" max="18" width="8.66666666666667" style="1" customWidth="1"/>
+    <col min="19" max="19" width="14.4444444444444" style="1" customWidth="1"/>
+    <col min="20" max="20" width="13.7777777777778" style="1" customWidth="1"/>
+    <col min="21" max="21" width="8.44444444444444" style="1" customWidth="1"/>
+    <col min="22" max="22" width="14.8888888888889" style="1" customWidth="1"/>
+    <col min="23" max="23" width="21" style="1" customWidth="1"/>
+    <col min="24" max="25" width="12.5555555555556" style="1" customWidth="1"/>
+    <col min="26" max="26" width="18.8888888888889" style="1" customWidth="1"/>
+    <col min="27" max="27" width="24.8888888888889" style="1" customWidth="1"/>
+    <col min="28" max="28" width="29.4444444444444" style="1" customWidth="1"/>
+    <col min="29" max="29" width="21.4444444444444" style="1" customWidth="1"/>
+    <col min="30" max="30" width="21.5555555555556" style="1" customWidth="1"/>
+    <col min="31" max="31" width="26.6666666666667" style="1" customWidth="1"/>
+    <col min="32" max="32" width="14.7777777777778" style="1" customWidth="1"/>
+    <col min="33" max="33" width="21" style="1" customWidth="1"/>
+    <col min="34" max="34" width="23.2222222222222" style="1" customWidth="1"/>
+    <col min="35" max="35" width="24.2222222222222" style="1" customWidth="1"/>
+    <col min="36" max="37" width="20" style="1" customWidth="1"/>
+    <col min="38" max="38" width="13.1111111111111" style="1" customWidth="1"/>
+    <col min="39" max="39" width="25.6666666666667" style="1" customWidth="1"/>
+    <col min="40" max="40" width="25.7777777777778" style="1" customWidth="1"/>
+    <col min="41" max="41" width="20.8888888888889" style="1" customWidth="1"/>
+    <col min="42" max="42" width="22.5555555555556" style="1" customWidth="1"/>
+    <col min="43" max="43" width="25.1111111111111" style="1" customWidth="1"/>
+    <col min="44" max="44" width="21.7777777777778" style="1" customWidth="1"/>
+    <col min="45" max="45" width="23.2222222222222" style="1" customWidth="1"/>
+    <col min="46" max="46" width="15.1111111111111" style="1" customWidth="1"/>
+    <col min="47" max="47" width="24.1111111111111" style="1" customWidth="1"/>
+    <col min="48" max="48" width="27.4444444444444" style="1" customWidth="1"/>
+    <col min="49" max="49" width="22.7777777777778" style="1" customWidth="1"/>
+    <col min="50" max="50" width="20.4444444444444" style="1" customWidth="1"/>
+    <col min="51" max="51" width="22.5555555555556" style="1" customWidth="1"/>
+    <col min="52" max="52" width="28.8888888888889" style="1" customWidth="1"/>
+    <col min="53" max="53" width="11.6666666666667" style="1" customWidth="1"/>
+    <col min="54" max="54" width="12" style="1" customWidth="1"/>
+    <col min="55" max="55" width="16.5555555555556" style="1" customWidth="1"/>
+    <col min="56" max="56" width="20" style="1" customWidth="1"/>
+    <col min="57" max="57" width="19.7777777777778" style="1" customWidth="1"/>
+    <col min="58" max="58" width="25.8888888888889" style="1" customWidth="1"/>
+    <col min="59" max="59" width="19" style="1" customWidth="1"/>
+    <col min="60" max="61" width="18.6666666666667" style="1" customWidth="1"/>
+    <col min="62" max="62" width="20.6666666666667" style="1" customWidth="1"/>
+    <col min="63" max="63" width="27.7777777777778" style="1" customWidth="1"/>
+    <col min="64" max="64" width="55.8888888888889" style="1" customWidth="1"/>
+    <col min="65" max="65" width="45" style="1" customWidth="1"/>
+    <col min="66" max="66" width="61.5555555555556" style="1" customWidth="1"/>
+    <col min="67" max="67" width="10.7777777777778" style="1" customWidth="1"/>
+    <col min="68" max="68" width="21.6666666666667" style="1" customWidth="1"/>
+    <col min="69" max="70" width="18.1111111111111" style="1" customWidth="1"/>
+    <col min="71" max="71" width="18.5555555555556" style="1" customWidth="1"/>
+    <col min="72" max="72" width="8.44444444444444" style="1" customWidth="1"/>
+    <col min="73" max="73" width="9.66666666666667" style="1" customWidth="1"/>
+    <col min="74" max="74" width="11.6666666666667" style="1" customWidth="1"/>
+    <col min="75" max="75" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="76" max="76" width="16.8888888888889" style="1" customWidth="1"/>
+    <col min="77" max="77" width="12.6666666666667" style="1" customWidth="1"/>
+    <col min="78" max="78" width="17.8888888888889" style="1" customWidth="1"/>
+    <col min="79" max="79" width="24.1111111111111" style="1" customWidth="1"/>
+    <col min="80" max="80" width="26.4444444444444" style="1" customWidth="1"/>
+    <col min="81" max="81" width="27.4444444444444" style="1" customWidth="1"/>
+    <col min="82" max="83" width="23.1111111111111" style="1" customWidth="1"/>
+    <col min="84" max="84" width="21.8888888888889" style="1" customWidth="1"/>
+    <col min="85" max="85" width="26.4444444444444" style="1" customWidth="1"/>
+    <col min="86" max="86" width="22.4444444444444" style="1" customWidth="1"/>
+    <col min="87" max="87" width="26.7777777777778" style="1" customWidth="1"/>
+    <col min="88" max="88" width="13.2222222222222" style="1" customWidth="1"/>
+    <col min="89" max="89" width="17.7777777777778" style="1" customWidth="1"/>
+    <col min="90" max="90" width="23" style="1" customWidth="1"/>
+    <col min="91" max="91" width="13.2222222222222" style="1" customWidth="1"/>
+    <col min="92" max="92" width="14.4444444444444" style="1" customWidth="1"/>
+    <col min="93" max="93" width="22.8888888888889" style="1" customWidth="1"/>
+    <col min="94" max="94" width="20.5555555555556" style="1" customWidth="1"/>
+    <col min="95" max="95" width="24.4444444444444" style="1" customWidth="1"/>
+    <col min="96" max="96" width="31.7777777777778" style="1" customWidth="1"/>
+    <col min="97" max="97" width="42.1111111111111" style="1" customWidth="1"/>
+    <col min="98" max="98" width="28.8888888888889" style="1" customWidth="1"/>
+    <col min="99" max="99" width="23.7777777777778" style="1" customWidth="1"/>
+    <col min="100" max="100" width="28.8888888888889" style="1" customWidth="1"/>
+    <col min="101" max="101" width="19.7777777777778" style="1" customWidth="1"/>
+    <col min="102" max="102" width="14.7777777777778" style="1" customWidth="1"/>
+    <col min="103" max="103" width="16.7777777777778" style="1" customWidth="1"/>
+    <col min="104" max="104" width="21" style="1" customWidth="1"/>
+    <col min="105" max="105" width="22.7777777777778" style="1" customWidth="1"/>
+    <col min="106" max="107" width="24.7777777777778" style="1" customWidth="1"/>
+    <col min="108" max="108" width="19.8888888888889" style="1" customWidth="1"/>
+    <col min="109" max="109" width="20.1111111111111" style="1" customWidth="1"/>
+    <col min="110" max="110" width="20.5555555555556" style="1" customWidth="1"/>
+    <col min="111" max="111" width="25" style="1" customWidth="1"/>
+    <col min="112" max="112" width="25.6666666666667" style="1" customWidth="1"/>
+    <col min="113" max="113" width="25.4444444444444" style="1" customWidth="1"/>
+    <col min="114" max="114" width="20.1111111111111" style="1" customWidth="1"/>
+    <col min="115" max="115" width="22.1111111111111" style="1" customWidth="1"/>
+    <col min="116" max="116" width="17.6666666666667" style="1" customWidth="1"/>
+    <col min="117" max="117" width="15" style="1" customWidth="1"/>
+    <col min="118" max="118" width="19.5555555555556" style="1" customWidth="1"/>
+    <col min="119" max="119" width="14.2222222222222" style="1" customWidth="1"/>
+    <col min="120" max="120" width="16.2222222222222" style="1" customWidth="1"/>
+    <col min="121" max="121" width="24.2222222222222" style="1" customWidth="1"/>
+    <col min="122" max="122" width="30.5555555555556" style="1" customWidth="1"/>
+    <col min="123" max="123" width="32.7777777777778" style="1" customWidth="1"/>
+    <col min="124" max="124" width="33.7777777777778" style="1" customWidth="1"/>
+    <col min="125" max="126" width="29.5555555555556" style="1" customWidth="1"/>
+    <col min="127" max="127" width="16.7777777777778" style="1" customWidth="1"/>
+    <col min="128" max="128" width="17" style="1" customWidth="1"/>
+    <col min="129" max="129" width="19" style="1" customWidth="1"/>
+    <col min="130" max="130" width="30.1111111111111" style="1" customWidth="1"/>
+    <col min="131" max="131" width="22.7777777777778" style="1" customWidth="1"/>
+    <col min="132" max="132" width="24.6666666666667" style="1" customWidth="1"/>
+    <col min="133" max="133" width="21.7777777777778" style="1" customWidth="1"/>
+    <col min="134" max="134" width="21.6666666666667" style="1" customWidth="1"/>
+    <col min="135" max="16384" width="9.11111111111111" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:127">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="C1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
+      <c r="G1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA1" s="1"/>
+      <c r="AB1" s="1"/>
+      <c r="AC1" s="1"/>
+      <c r="AD1" s="1"/>
+      <c r="AE1" s="1"/>
+      <c r="AF1" s="1"/>
+      <c r="AG1" s="1"/>
+      <c r="AH1" s="1"/>
+      <c r="AI1" s="1"/>
+      <c r="AJ1" s="1"/>
+      <c r="AK1" s="1"/>
+      <c r="AL1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AN1" s="1"/>
+      <c r="AO1" s="1"/>
+      <c r="AP1" s="1"/>
+      <c r="AQ1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AR1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AS1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AT1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AU1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AV1" s="1"/>
+      <c r="AW1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AX1" s="1"/>
+      <c r="AY1" s="1"/>
+      <c r="AZ1" s="1"/>
+      <c r="BA1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="BB1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="BC1" s="2"/>
+      <c r="BD1" s="2"/>
+      <c r="BE1" s="2"/>
+      <c r="BF1" s="2"/>
+      <c r="BG1" s="2"/>
+      <c r="BH1" s="2"/>
+      <c r="BI1" s="2"/>
+      <c r="BJ1" s="2"/>
+      <c r="BK1" s="2"/>
+      <c r="BL1" s="2"/>
+      <c r="BM1" s="2"/>
+      <c r="BN1" s="2"/>
+      <c r="BO1" s="2"/>
+      <c r="BP1" s="2"/>
+      <c r="BQ1" s="2"/>
+      <c r="BR1" s="2"/>
+      <c r="BS1" s="2"/>
+      <c r="BT1" s="2"/>
+      <c r="BU1" s="2"/>
+      <c r="BV1" s="2"/>
+      <c r="BW1" s="2"/>
+      <c r="BX1" s="2"/>
+      <c r="BY1" s="2"/>
+      <c r="BZ1" s="2"/>
+      <c r="CA1" s="2"/>
+      <c r="CB1" s="2"/>
+      <c r="CC1" s="2"/>
+      <c r="CD1" s="2"/>
+      <c r="CE1" s="2"/>
+      <c r="CF1" s="2"/>
+      <c r="CG1" s="2"/>
+      <c r="CH1" s="2"/>
+      <c r="CI1" s="2"/>
+      <c r="CJ1" s="2"/>
+      <c r="CK1" s="2"/>
+      <c r="CL1" s="2"/>
+      <c r="CM1" s="2"/>
+      <c r="CN1" s="2"/>
+      <c r="CO1" s="2"/>
+      <c r="CP1" s="2"/>
+      <c r="CQ1" s="2"/>
+      <c r="CR1" s="2"/>
+      <c r="CS1" s="2"/>
+      <c r="CT1" s="2"/>
+      <c r="CU1" s="2"/>
+      <c r="CV1" s="2"/>
+      <c r="CW1" s="2"/>
+      <c r="CX1" s="2"/>
+      <c r="CY1" s="2"/>
+      <c r="CZ1" s="2"/>
+      <c r="DA1" s="2"/>
+      <c r="DB1" s="2"/>
+      <c r="DC1" s="2"/>
+      <c r="DD1" s="2"/>
+      <c r="DE1" s="2"/>
+      <c r="DF1" s="2"/>
+      <c r="DG1" s="2"/>
+      <c r="DH1" s="2"/>
+      <c r="DI1" s="2"/>
+      <c r="DJ1" s="2"/>
+      <c r="DK1" s="2"/>
+      <c r="DL1" s="2"/>
+      <c r="DM1" s="2"/>
+      <c r="DN1" s="2"/>
+      <c r="DO1" s="2"/>
+      <c r="DP1" s="2"/>
+      <c r="DQ1" s="2"/>
+      <c r="DR1" s="2"/>
+      <c r="DS1" s="2"/>
+      <c r="DT1" s="2"/>
+      <c r="DU1" s="2"/>
+      <c r="DV1" s="2"/>
+      <c r="DW1" s="2"/>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:134">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -1157,122 +2033,1586 @@
       <c r="K2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="L2" t="s">
+      <c r="L2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="V2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="W2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="X2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AM2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AN2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AO2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AP2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AQ2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AR2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AS2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AT2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AU2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AV2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AW2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AX2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AY2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AZ2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="BA2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="BB2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="BC2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="BD2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="BE2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="BF2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="BG2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="BH2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="BI2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="BJ2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="BK2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="BL2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="BM2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="BN2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="BO2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="BP2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="BQ2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="BR2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="BS2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="BT2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="BU2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="BV2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="BW2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="BX2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="BY2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="BZ2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="CA2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="CB2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="CC2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="CD2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="CE2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="CF2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="CG2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="CH2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="CI2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="CJ2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="CK2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="CL2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="CM2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="CN2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="CO2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="CP2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="CQ2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="CR2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="CS2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="CT2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="CU2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="CV2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="CW2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="CX2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="CY2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="CZ2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="DA2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="DB2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="DC2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="DD2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="DE2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="DF2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="DG2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="DH2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="DI2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="DJ2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="DK2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="DL2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="DM2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="DN2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="DO2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="DP2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="DQ2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="DR2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="DS2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="DT2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="DU2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="DV2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="DW2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="DX2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="DY2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="DZ2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="EA2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="EB2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="EC2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="ED2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:134">
+      <c r="A3" s="1">
+        <v>0</v>
+      </c>
+      <c r="B3" s="1">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="D3" s="1">
         <v>3</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="E3" s="1">
         <v>4</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="F3" s="1">
         <v>5</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="G3" s="1">
         <v>6</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="H3" s="1">
         <v>7</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="I3" s="1">
         <v>8</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="J3" s="1">
         <v>9</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="K3" s="1">
         <v>10</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="L3" s="1">
         <v>11</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="M3" s="1">
         <v>12</v>
       </c>
-      <c r="L3">
+      <c r="N3" s="1">
+        <v>13</v>
+      </c>
+      <c r="O3" s="1">
+        <v>14</v>
+      </c>
+      <c r="P3" s="1">
+        <v>15</v>
+      </c>
+      <c r="Q3" s="1">
+        <v>16</v>
+      </c>
+      <c r="R3" s="1">
+        <v>17</v>
+      </c>
+      <c r="S3" s="1">
+        <v>18</v>
+      </c>
+      <c r="T3" s="1">
+        <v>19</v>
+      </c>
+      <c r="U3" s="1">
+        <v>20</v>
+      </c>
+      <c r="V3" s="1">
+        <v>21</v>
+      </c>
+      <c r="W3" s="1">
+        <v>22</v>
+      </c>
+      <c r="X3" s="1">
+        <v>23</v>
+      </c>
+      <c r="Y3" s="1">
+        <v>24</v>
+      </c>
+      <c r="Z3" s="1">
+        <v>25</v>
+      </c>
+      <c r="AA3" s="1">
+        <v>26</v>
+      </c>
+      <c r="AB3" s="1">
+        <v>27</v>
+      </c>
+      <c r="AC3" s="1">
+        <v>28</v>
+      </c>
+      <c r="AD3" s="1">
+        <v>29</v>
+      </c>
+      <c r="AE3" s="1">
+        <v>30</v>
+      </c>
+      <c r="AF3" s="1">
+        <v>31</v>
+      </c>
+      <c r="AG3" s="1">
+        <v>32</v>
+      </c>
+      <c r="AH3" s="1">
+        <v>33</v>
+      </c>
+      <c r="AI3" s="1">
+        <v>34</v>
+      </c>
+      <c r="AJ3" s="1">
+        <v>35</v>
+      </c>
+      <c r="AK3" s="1">
+        <v>36</v>
+      </c>
+      <c r="AL3" s="1">
+        <v>37</v>
+      </c>
+      <c r="AM3" s="1">
+        <v>38</v>
+      </c>
+      <c r="AN3" s="1">
+        <v>39</v>
+      </c>
+      <c r="AO3" s="1">
+        <v>40</v>
+      </c>
+      <c r="AP3" s="1">
+        <v>41</v>
+      </c>
+      <c r="AQ3" s="1">
+        <v>42</v>
+      </c>
+      <c r="AR3" s="1">
+        <v>43</v>
+      </c>
+      <c r="AS3" s="1">
+        <v>44</v>
+      </c>
+      <c r="AT3" s="1">
+        <v>45</v>
+      </c>
+      <c r="AU3" s="1">
+        <v>46</v>
+      </c>
+      <c r="AV3" s="1">
+        <v>47</v>
+      </c>
+      <c r="AW3" s="1">
+        <v>48</v>
+      </c>
+      <c r="AX3" s="1">
+        <v>49</v>
+      </c>
+      <c r="AY3" s="1">
+        <v>50</v>
+      </c>
+      <c r="AZ3" s="1">
+        <v>51</v>
+      </c>
+      <c r="BA3" s="1">
+        <v>52</v>
+      </c>
+      <c r="BB3" s="1">
+        <v>53</v>
+      </c>
+      <c r="BC3" s="1">
+        <v>54</v>
+      </c>
+      <c r="BD3" s="1">
+        <v>55</v>
+      </c>
+      <c r="BE3" s="1">
+        <v>56</v>
+      </c>
+      <c r="BF3" s="1">
+        <v>57</v>
+      </c>
+      <c r="BG3" s="1">
+        <v>58</v>
+      </c>
+      <c r="BH3" s="1">
+        <v>59</v>
+      </c>
+      <c r="BI3" s="1">
+        <v>60</v>
+      </c>
+      <c r="BJ3" s="1">
+        <v>61</v>
+      </c>
+      <c r="BK3" s="1">
+        <v>62</v>
+      </c>
+      <c r="BL3" s="1">
+        <v>63</v>
+      </c>
+      <c r="BM3" s="1">
+        <v>64</v>
+      </c>
+      <c r="BN3" s="1">
+        <v>65</v>
+      </c>
+      <c r="BO3" s="1">
+        <v>66</v>
+      </c>
+      <c r="BP3" s="1">
+        <v>67</v>
+      </c>
+      <c r="BQ3" s="1">
+        <v>68</v>
+      </c>
+      <c r="BR3" s="1">
+        <v>69</v>
+      </c>
+      <c r="BS3" s="1">
+        <v>70</v>
+      </c>
+      <c r="BT3" s="1">
+        <v>71</v>
+      </c>
+      <c r="BU3" s="1">
+        <v>72</v>
+      </c>
+      <c r="BV3" s="1">
+        <v>73</v>
+      </c>
+      <c r="BW3" s="1">
+        <v>74</v>
+      </c>
+      <c r="BX3" s="1">
+        <v>75</v>
+      </c>
+      <c r="BY3" s="1">
+        <v>76</v>
+      </c>
+      <c r="BZ3" s="1">
+        <v>77</v>
+      </c>
+      <c r="CA3" s="1">
+        <v>78</v>
+      </c>
+      <c r="CB3" s="1">
+        <v>79</v>
+      </c>
+      <c r="CC3" s="1">
+        <v>80</v>
+      </c>
+      <c r="CD3" s="1">
+        <v>81</v>
+      </c>
+      <c r="CE3" s="1">
+        <v>82</v>
+      </c>
+      <c r="CF3" s="1">
+        <v>83</v>
+      </c>
+      <c r="CG3" s="1">
+        <v>84</v>
+      </c>
+      <c r="CH3" s="1">
+        <v>85</v>
+      </c>
+      <c r="CI3" s="1">
+        <v>86</v>
+      </c>
+      <c r="CJ3" s="1">
+        <v>87</v>
+      </c>
+      <c r="CK3" s="1">
+        <v>88</v>
+      </c>
+      <c r="CL3" s="1">
+        <v>89</v>
+      </c>
+      <c r="CM3" s="1">
+        <v>90</v>
+      </c>
+      <c r="CN3" s="1">
+        <v>91</v>
+      </c>
+      <c r="CO3" s="1">
+        <v>92</v>
+      </c>
+      <c r="CP3" s="1">
+        <v>93</v>
+      </c>
+      <c r="CQ3" s="1">
+        <v>94</v>
+      </c>
+      <c r="CR3" s="1">
+        <v>95</v>
+      </c>
+      <c r="CS3" s="1">
+        <v>96</v>
+      </c>
+      <c r="CT3" s="1">
+        <v>97</v>
+      </c>
+      <c r="CU3" s="1">
+        <v>98</v>
+      </c>
+      <c r="CV3" s="1">
+        <v>99</v>
+      </c>
+      <c r="CW3" s="1">
+        <v>100</v>
+      </c>
+      <c r="CX3" s="1">
+        <v>101</v>
+      </c>
+      <c r="CY3" s="1">
+        <v>102</v>
+      </c>
+      <c r="CZ3" s="1">
+        <v>103</v>
+      </c>
+      <c r="DA3" s="1">
+        <v>104</v>
+      </c>
+      <c r="DB3" s="1">
+        <v>105</v>
+      </c>
+      <c r="DC3" s="1">
+        <v>106</v>
+      </c>
+      <c r="DD3" s="1">
+        <v>107</v>
+      </c>
+      <c r="DE3" s="1">
+        <v>108</v>
+      </c>
+      <c r="DF3" s="1">
+        <v>109</v>
+      </c>
+      <c r="DG3" s="1">
+        <v>110</v>
+      </c>
+      <c r="DH3" s="1">
+        <v>111</v>
+      </c>
+      <c r="DI3" s="1">
+        <v>112</v>
+      </c>
+      <c r="DJ3" s="1">
+        <v>113</v>
+      </c>
+      <c r="DK3" s="1">
+        <v>114</v>
+      </c>
+      <c r="DL3" s="1">
+        <v>115</v>
+      </c>
+      <c r="DM3" s="1">
+        <v>116</v>
+      </c>
+      <c r="DN3" s="1">
+        <v>117</v>
+      </c>
+      <c r="DO3" s="1">
+        <v>118</v>
+      </c>
+      <c r="DP3" s="1">
+        <v>119</v>
+      </c>
+      <c r="DQ3" s="1">
+        <v>120</v>
+      </c>
+      <c r="DR3" s="1">
+        <v>121</v>
+      </c>
+      <c r="DS3" s="1">
+        <v>122</v>
+      </c>
+      <c r="DT3" s="1">
+        <v>123</v>
+      </c>
+      <c r="DU3" s="1">
+        <v>124</v>
+      </c>
+      <c r="DV3" s="1">
+        <v>125</v>
+      </c>
+      <c r="DW3" s="1">
+        <v>126</v>
+      </c>
+      <c r="DX3" s="1">
+        <v>127</v>
+      </c>
+      <c r="DY3" s="1">
+        <v>128</v>
+      </c>
+      <c r="DZ3" s="1">
+        <v>129</v>
+      </c>
+      <c r="EA3" s="1">
+        <v>130</v>
+      </c>
+      <c r="EB3" s="1">
+        <v>131</v>
+      </c>
+      <c r="EC3" s="1">
+        <v>132</v>
+      </c>
+      <c r="ED3" s="1">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="4" spans="1:134">
+      <c r="A4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J4" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="K4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="R4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="S4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="T4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="U4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="V4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="W4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="X4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z4" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA4" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AB4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AC4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AD4" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AE4" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AF4" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AG4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AH4" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AI4" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ4" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AK4" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AL4" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AM4" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AN4" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AO4" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AP4" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AQ4" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AR4" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AS4" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AT4" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AU4" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AV4" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AW4" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AX4" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="AY4" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="AZ4" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="BA4" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="BB4" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="BC4" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="BD4" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="BE4" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="BF4" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="BG4" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="BH4" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="BI4" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="BJ4" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="BK4" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="BL4" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="BM4" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="BN4" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="BO4" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="BP4" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="BQ4" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="BR4" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="BS4" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="BT4" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="BU4" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="BV4" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="BW4" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="BX4" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="BY4" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="BZ4" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="CA4" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="CB4" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="CC4" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="CD4" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="CE4" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="CF4" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="CG4" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="CH4" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="CI4" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="CJ4" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="CK4" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="CL4" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="CM4" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="CN4" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="CO4" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="CP4" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="CQ4" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="CR4" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="CS4" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="CT4" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="CU4" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="CV4" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="CW4" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="CX4" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="CY4" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="CZ4" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="DA4" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="DB4" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="DC4" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="DD4" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="DE4" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="DF4" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="DG4" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="DH4" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="DI4" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="DJ4" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="DK4" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="DL4" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="DM4" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="DN4" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="DO4" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="DP4" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="DQ4" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="DR4" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="DS4" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="DT4" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="DU4" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="DV4" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="DW4" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="DX4" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="DY4" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="DZ4" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="EA4" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="EB4" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="EC4" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="ED4" s="1" t="s">
+        <v>134</v>
+      </c>
     </row>
-    <row r="4" spans="1:12">
-      <c r="A4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="L4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:134">
       <c r="A5" s="1" t="s">
-        <v>25</v>
+        <v>135</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>26</v>
+        <v>136</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>27</v>
+        <v>137</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>28</v>
+        <v>138</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>29</v>
+        <v>139</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>30</v>
+        <v>140</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>31</v>
+        <v>141</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>32</v>
+        <v>142</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>33</v>
+        <v>143</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>34</v>
+        <v>144</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="L5" t="s">
-        <v>36</v>
+        <v>145</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="P5" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q5" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="R5" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="S5" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="T5" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="U5" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="V5" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="W5" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="X5" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="Y5" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="Z5" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="AA5" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="AB5" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="AC5" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="AD5" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="AE5" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="AF5" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="AG5" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="AH5" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="AI5" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="AJ5" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="AK5" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="AL5" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="AM5" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="AN5" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="AO5" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="AP5" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="AQ5" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="AR5" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="AS5" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="AT5" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="AU5" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="AV5" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="AW5" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="AX5" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="AY5" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="AZ5" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="BA5" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="BB5" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="BC5" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="BD5" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="BE5" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="BF5" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="BG5" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="BH5" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="BI5" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="BJ5" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="BK5" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="BL5" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="BM5" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="BN5" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="BO5" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="BP5" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="BQ5" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="BR5" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="BS5" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="BT5" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="BU5" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="BV5" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="BW5" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="BX5" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="BY5" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="BZ5" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="CA5" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="CB5" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="CC5" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="CD5" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="CE5" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="CF5" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="CG5" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="CH5" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="CI5" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="CJ5" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="CK5" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="CL5" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="CM5" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="CN5" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="CO5" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="CP5" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="CQ5" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="CR5" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="CS5" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="CT5" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="CU5" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="CV5" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="CW5" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="CX5" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="CY5" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="CZ5" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="DA5" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="DB5" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="DC5" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="DD5" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="DE5" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="DF5" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="DG5" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="DH5" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="DI5" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="DJ5" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="DK5" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="DL5" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="DM5" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="DN5" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="DO5" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="DP5" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="DQ5" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="DR5" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="DS5" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="DT5" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="DU5" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="DV5" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="DW5" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="DX5" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="DY5" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="DZ5" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="EA5" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="EB5" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="EC5" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="ED5" s="1" t="s">
+        <v>234</v>
       </c>
     </row>
   </sheetData>
